--- a/outputs/evaluation/architecture/CF_M05_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,72 +481,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M05_AU06</t>
+          <t>CF_M05_AU08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>SonarQube</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>The client, also called the frontEnd, is responsible for the presentation and user experience
-of the application by encapsulating the interface logic and coordinating the calls to the server
-API.</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>62</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CF_M05_AD02</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Internet</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Network medium for user access.</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>0.0296</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CF_M05_AU08</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SonarQube</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
         <is>
           <t>SonarQube is a
 web application that statically analyses the code and offers recommendations and statistics
@@ -554,8 +502,58 @@
 problems, the amount of code covered in the tests, code duplication and code smells.</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>84</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CF_M05_AU37</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>The end user of the portal and applications.</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CF_M05_AU09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Grafana</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
+        </is>
+      </c>
       <c r="E3" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -566,82 +564,79 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
+          <t>AU_23</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Data format for communication.</t>
+          <t>The Portal Service communicates with the Leader Service for traffic routing and security.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.0604</v>
+        <v>0.0195</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AU09</t>
+          <t>CF_M05_AU11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grafana</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
+          <t>These two microservices are responsible for
+calls to external services related to car sales.</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M05_AU37</t>
+          <t>CF_M05_AD01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Spring Boot</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>The end user of the system, including business users, support staff, and administrators.</t>
+          <t>Backend framework used for the server-side application.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.2069</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AU11</t>
+          <t>CF_M05_AU12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>GSB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -667,230 +662,227 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_24</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Spring Boot</t>
+          <t>User</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Backend framework for building microservices.</t>
+          <t>The end user of the portal and applications.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.2108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AU12</t>
+          <t>CF_M05_AU16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GSB</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>These two microservices are responsible for
-calls to external services related to car sales.</t>
+          <t>the microservices are connected to a shared database that is decoupled per
+microservice and client. There is a schema for each microservice and each client has its
+own set of schemas per microservice.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M05_AD01</t>
+          <t>CF_M05_AD06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>The end user of the system, including business users, support staff, and administrators.</t>
+          <t>The Portal Service communicates with Amazon RDS for data persistence.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.0968</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M05_AU16</t>
+          <t>CF_M05_AU18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Business Logic Layer (Services)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>the microservices are connected to a shared database that is decoupled per
-microservice and client. There is a schema for each microservice and each client has its
-own set of schemas per microservice.</t>
+          <t>Services provide the interface and implementation of all the application's business logic.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M05_AD06</t>
+          <t>CF_M05_AD04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Data Access Layer</t>
+          <t>Server Layer (Backend)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Repository layer interacting with the database.</t>
+          <t>Handles business logic, security, and data persistence.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.2117</v>
+        <v>0.1622</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>CF_M05_AU19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Domain Layer (Models)</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leader microservice communicates with Scheduler microservice. </t>
+          <t>Models represent the internal and persistent structure of the system entities, reflecting the
+stored information identically.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M05_AU01, CF_M05_AU05</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>leader microservice, scheduler microservice</t>
-        </is>
-      </c>
+          <t>CF_M05_AD04</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>MVVM (Model-View-ViewModel)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>The system is divided into small, independent, and autonomous services where each microservice is responsible for a specific functionality and communicates with others via messaging systems.</t>
+          <t>Used in the Angular frontend, this pattern separates the user interface (View) from the logic and data processing (ViewModel) and the data contract (Model).</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.5749</v>
+        <v>0.1898</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M05_AU25</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>CF_M05_AU20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Contract Layer (DTO/Mappers)</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">It can be observed that leader microservice communicates with Communication Log microservice. </t>
+          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
+request to be structured, providing a customized format based on response requirements.</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M05_AU01, CF_M05_AU03</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>leader microservice, access control microservice</t>
-        </is>
-      </c>
+          <t>CF_M05_AD04</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Communication Log</t>
+          <t>DTO / Mapper</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Service that records all system communications for traceability and auditing.</t>
+          <t>Handles data transfer objects and conversion between models and external representations.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.592</v>
+        <v>0.2503</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M05_AU27</t>
+          <t>CF_M05_AU25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -901,46 +893,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Portal microservice communicates with the frontend indirectly through the Leader microservice</t>
+          <t xml:space="preserve">It can be observed that leader microservice communicates with Communication Log microservice. </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M05_AU02, CF_M05_AU17</t>
+          <t>CF_M05_AU01, CF_M05_AU03</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>portal microservice, presentation layer (controllers)</t>
+          <t>leader microservice, access control microservice</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
+          <t>AU_26</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>The system is divided into small, independent, and autonomous services where each microservice is responsible for a specific functionality and communicates with others via messaging systems.</t>
+          <t>The Leader Service communicates with the Communication Log Service.</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.4374</v>
+        <v>0.6552</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M05_AU28</t>
+          <t>CF_M05_AU27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -951,44 +939,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>Portal microservice communicates with the frontend indirectly through the Leader microservice</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>57</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CF_M05_AU14, CF_M05_AU13</t>
+          <t>CF_M05_AU02, CF_M05_AU17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>viewmodel, view</t>
+          <t>portal microservice, presentation layer (controllers)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ViewModel</t>
-        </is>
-      </c>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Frontend component managing behavior, data processing, and service orchestration.</t>
+          <t>The Leader Service communicates with the Portal Service.</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.5286</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M05_AU29</t>
+          <t>CF_M05_AU28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1005,18 +991,18 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CF_M05_AU14, CF_M05_AU15</t>
+          <t>CF_M05_AU14, CF_M05_AU13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>viewmodel, model</t>
+          <t>viewmodel, view</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1026,11 +1012,11 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Frontend component managing behavior, data processing, and service orchestration.</t>
+          <t>TypeScript files and services that process data and orchestrate HTTP calls.</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.4976</v>
       </c>
     </row>
     <row r="13">
@@ -1062,21 +1048,17 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Access Control</t>
-        </is>
-      </c>
+          <t>AU_34</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Service responsible for user authentication, authorization, and role management.</t>
+          <t>The ViewModel component sends HTTP requests to the Controller component.</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.1174</v>
+        <v>0.3278</v>
       </c>
     </row>
     <row r="14">
@@ -1106,116 +1088,159 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Data Access Layer</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Repository layer interacting with the database.</t>
+          <t>Handles database access and queries.</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.0654</v>
+        <v>0.2747</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CF_M05_AU37</t>
+          <t>CF_M05_AU32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
-responsibilities are separated:</t>
+          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
+structure and normalize communication with the data layer. </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CF_M05_AD02</t>
+          <t>CF_M05_AU17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AU_09</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>AU_19</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Connection between User and Internet.</t>
+          <t>Handles database access and queries.</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.0133</v>
+        <v>0.0446</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CF_M05_AD06</t>
+          <t>CF_M05_AU35</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Shared Database</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>the microservices are connected to a shared database that is decoupled per
-microservice and client. There is a schema for each microservice and each client has its
-own set of schemas per microservice.</t>
+          <t>The message
+exchange protocol used in this case is HTTP</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Data Access Layer</t>
-        </is>
-      </c>
+          <t>AU_34</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Repository layer interacting with the database.</t>
+          <t>The ViewModel component sends HTTP requests to the Controller component.</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.1518</v>
+        <v>0.2704</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Shared Database</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>the microservices are connected to a shared database that is decoupled per
+microservice and client. There is a schema for each microservice and each client has its
+own set of schemas per microservice.</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>60</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AU_31</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>The Portal Service communicates with Amazon RDS for data persistence.</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0687</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,20 +481,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CF_M05_AU06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>The client, also called the frontEnd, is responsible for the presentation and user experience
+of the application by encapsulating the interface logic and coordinating the calls to the server
+API.</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>62</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>The Access Control Service reads from and writes to Amazon RDS.</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0819</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>CF_M05_AU08</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>SonarQube</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>SonarQube is a
 web application that statically analyses the code and offers recommendations and statistics
@@ -502,58 +550,8 @@
 problems, the amount of code covered in the tests, code duplication and code smells.</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E3" t="n">
         <v>84</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CF_M05_AU37</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>The end user of the portal and applications.</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CF_M05_AU09</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Grafana</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>87</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -564,79 +562,82 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>The Portal Service communicates with the Leader Service for traffic routing and security.</t>
+          <t>The end user of the portal and applications.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.0195</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M05_AU11</t>
+          <t>CF_M05_AU09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Grafana</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>These two microservices are responsible for
-calls to external services related to car sales.</t>
+          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M05_AD01</t>
+          <t>CF_M05_AU37</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Spring Boot</t>
+          <t>User</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Backend framework used for the server-side application.</t>
+          <t>The end user of the portal and applications.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.2069</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AU12</t>
+          <t>CF_M05_AU11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GSB</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -655,234 +656,233 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M05_AD01</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Spring Boot</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>The end user of the portal and applications.</t>
+          <t>Backend framework used for developing microservices and REST APIs.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.2125</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>CF_M05_AU12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GSB</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>These two microservices are responsible for
+calls to external services related to car sales.</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CF_M05_P01</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>The end user of the portal and applications.</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>CF_M05_AU16</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Database</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>61</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CF_M05_AD06</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>AU_31</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>The Portal Service communicates with Amazon RDS for data persistence.</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0.0968</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CF_M05_AU18</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Business Logic Layer (Services)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Services provide the interface and implementation of all the application's business logic.</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>70</v>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
+          <t>CF_M05_P06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Server Layer (Backend)</t>
+          <t>Data Access Layer (Repository)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Handles business logic, security, and data persistence.</t>
+          <t>Backend layer interacting with the database.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.1622</v>
+        <v>0.1214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M05_AU19</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Domain Layer (Models)</t>
-        </is>
-      </c>
+          <t>CF_M05_AU25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Models represent the internal and persistent structure of the system entities, reflecting the
-stored information identically.</t>
+          <t xml:space="preserve">It can be observed that leader microservice communicates with Communication Log microservice. </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>CF_M05_AU01, CF_M05_AU03</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>leader microservice, access control microservice</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>MVVM (Model-View-ViewModel)</t>
-        </is>
-      </c>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Used in the Angular frontend, this pattern separates the user interface (View) from the logic and data processing (ViewModel) and the data contract (Model).</t>
+          <t>The Leader Service routes communications to the Communication Log Service.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.1898</v>
+        <v>0.5965</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M05_AU20</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Contract Layer (DTO/Mappers)</t>
-        </is>
-      </c>
+          <t>CF_M05_AU27</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
-request to be structured, providing a customized format based on response requirements.</t>
+          <t>Portal microservice communicates with the frontend indirectly through the Leader microservice</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M05_AD04</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>CF_M05_AU02, CF_M05_AU17</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>portal microservice, presentation layer (controllers)</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>DTO / Mapper</t>
+          <t>Microservices</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Handles data transfer objects and conversion between models and external representations.</t>
+          <t>The system is divided into small, independent, and autonomous services where each microservice is responsible for a specific functionality and communicates with others via messaging systems.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.2503</v>
+        <v>0.4517</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M05_AU25</t>
+          <t>CF_M05_AU29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -893,42 +893,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">It can be observed that leader microservice communicates with Communication Log microservice. </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>56</v>
-      </c>
+          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M05_AU01, CF_M05_AU03</t>
+          <t>CF_M05_AU14, CF_M05_AU15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>leader microservice, access control microservice</t>
+          <t>viewmodel, model</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AU_26</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ViewModel</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>The Leader Service communicates with the Communication Log Service.</t>
+          <t>Frontend component responsible for logic, data processing, and service orchestration (TS).</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.6552</v>
+        <v>0.5221</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M05_AU27</t>
+          <t>CF_M05_AU30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -938,309 +940,266 @@
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>Portal microservice communicates with the frontend indirectly through the Leader microservice</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>57</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CF_M05_AU02, CF_M05_AU17</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>portal microservice, presentation layer (controllers)</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>The Leader Service communicates with the Portal Service.</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0.5286</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU28</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU14, CF_M05_AU13</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>viewmodel, view</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>AU_12</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ViewModel</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>TypeScript files and services that process data and orchestrate HTTP calls.</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>0.4976</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CF_M05_AU30</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
         <is>
           <t>The controllers, through specific
 functions, process the requests received, manage the validation of the information and channel
 the requests to the corresponding modules or services</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CF_AU17, CF_AU18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>The Leader Service routes communications to the Access Control Service.</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.2629</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU31</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> the Repositories are responsible for performing queries on the database.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CF_AU21, CF_AU16</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Data Access Layer (Repository)</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Backend layer interacting with the database.</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2089</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
+structure and normalize communication with the data layer. </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>69</v>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CF_AU17, CF_AU18</t>
+          <t>CF_M05_AU17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AU_34</t>
+          <t>AU_29</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>The ViewModel component sends HTTP requests to the Controller component.</t>
+          <t>The ViewModel orchestrates HTTP calls to the backend Presentation Layer.</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.3278</v>
+        <v>0.0424</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>CF_M05_AU35</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> the Repositories are responsible for performing queries on the database.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CF_AU21, CF_AU16</t>
-        </is>
-      </c>
+          <t>The message
+exchange protocol used in this case is HTTP</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>62</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AU_19</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Repository</t>
-        </is>
-      </c>
+          <t>AU_29</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Handles database access and queries.</t>
+          <t>The ViewModel orchestrates HTTP calls to the backend Presentation Layer.</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.2747</v>
+        <v>0.2782</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CF_M05_AU32</t>
+          <t>CF_M05_AU37</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>Server (Backend)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
-structure and normalize communication with the data layer. </t>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
+responsibilities are separated:</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CF_M05_AU17</t>
+          <t>CF_M05_P02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Handles database access and queries.</t>
+          <t>The application organizes code into two distinct components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.0446</v>
+        <v>0.2932</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CF_M05_AU35</t>
+          <t>CF_M05_P06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Shared Database</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>The message
-exchange protocol used in this case is HTTP</t>
+          <t>the microservices are connected to a shared database that is decoupled per
+microservice and client. There is a schema for each microservice and each client has its
+own set of schemas per microservice.</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AU_34</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Data Access Layer (Repository)</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>The ViewModel component sends HTTP requests to the Controller component.</t>
+          <t>Backend layer interacting with the database.</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.2704</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CF_M05_AD06</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Shared Database</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>the microservices are connected to a shared database that is decoupled per
-microservice and client. There is a schema for each microservice and each client has its
-own set of schemas per microservice.</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>AU_31</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>The Portal Service communicates with Amazon RDS for data persistence.</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>0.0687</v>
+        <v>0.0864</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval_gt_report.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Client(Frontend)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,36 +513,92 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>The Access Control Service reads from and writes to Amazon RDS.</t>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.0819</v>
+        <v>0.8405</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>CF_M05_AU07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
+which allows the use of Kubernetes (K8s), a container orchestration platform created by
+Google, without the need to install or maintain it. </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>81</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CF_M05_P05</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Amazon Web Services</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>El proveïdor per aquest projecte és Amazon Web Services el qual té un ampli catàleg de serveis i recursos cloud.</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7812</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>CF_M05_AU08</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>SonarQube</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>SonarQube is a
 web application that statically analyses the code and offers recommendations and statistics
@@ -550,339 +606,283 @@
 problems, the amount of code covered in the tests, code duplication and code smells.</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>84</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CF_M05_AU37</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>The end user of the portal and applications.</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CF_M05_AU09</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Grafana</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>87</v>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M05_AU37</t>
+          <t>CF_M05_AU32</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Kubernetes</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>The end user of the portal and applications.</t>
+          <t>Pel desplegament de l’aplicació s’ha fet ús d’Amazon EKS, un servei que ofereix AWS el qual permet utilitzar Kubernetes (K8s).</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AU11</t>
+          <t>CF_M05_AU09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Grafana</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>These two microservices are responsible for
-calls to external services related to car sales.</t>
+          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M05_P01</t>
+          <t>CF_M05_AU32</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Spring Boot</t>
+          <t>Kubernetes</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Backend framework used for developing microservices and REST APIs.</t>
+          <t>Pel desplegament de l’aplicació s’ha fet ús d’Amazon EKS, un servei que ofereix AWS el qual permet utilitzar Kubernetes (K8s).</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.2125</v>
+        <v>0.6829</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AU12</t>
+          <t>CF_M05_AU16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GSB</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>These two microservices are responsible for
-calls to external services related to car sales.</t>
+          <t>the microservices are connected to a shared database that is decoupled per
+microservice and client. There is a schema for each microservice and each client has its
+own set of schemas per microservice.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M05_P01</t>
+          <t>CF_M05_P06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Capa d’accés a dades</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>The end user of the portal and applications.</t>
+          <t>La capa d’accés a dades interactua amb la base de dades.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.7621</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M05_AU16</t>
+          <t>CF_M05_AU17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Presentation Layer (Controllers)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>the microservices are connected to a shared database that is decoupled per
-microservice and client. There is a schema for each microservice and each client has its
-own set of schemas per microservice.</t>
+          <t>The controllers, through specific
+functions, process the requests received, manage the validation of the information and channel
+the requests to the corresponding modules or services of the data layer.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M05_P06</t>
+          <t>CF_M05_P04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Data Access Layer (Repository)</t>
-        </is>
-      </c>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Backend layer interacting with the database.</t>
+          <t>La capa de presentació rep les peticions i construeix les respostes, la capa de lògica de negoci aplica les regles del domini, la capa d’accés a dades interactua amb la base de dades i la capa de domini defineix el model de dades. S’hi afegeix una capa transversal de contracte que separa el model intern de la representació externa de l’API.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.1214</v>
+        <v>0.7357</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M05_AU25</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>CF_M05_AU19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Domain Layer (Models)</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">It can be observed that leader microservice communicates with Communication Log microservice. </t>
+          <t>Models represent the internal and persistent structure of the system entities, reflecting the
+stored information identically.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M05_AU01, CF_M05_AU03</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>leader microservice, access control microservice</t>
-        </is>
-      </c>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AU_22</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>The Leader Service routes communications to the Communication Log Service.</t>
+          <t>La capa de presentació rep les peticions i construeix les respostes, la capa de lògica de negoci aplica les regles del domini, la capa d’accés a dades interactua amb la base de dades i la capa de domini defineix el model de dades. S’hi afegeix una capa transversal de contracte que separa el model intern de la representació externa de l’API.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.5965</v>
+        <v>0.7736</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M05_AU27</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>CF_M05_AU20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Contract Layer (DTO/Mappers)</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Portal microservice communicates with the frontend indirectly through the Leader microservice</t>
+          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
+request to be structured, providing a customized format based on response requirements.</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M05_AU02, CF_M05_AU17</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>portal microservice, presentation layer (controllers)</t>
-        </is>
-      </c>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>P_01</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Microservices</t>
-        </is>
-      </c>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>The system is divided into small, independent, and autonomous services where each microservice is responsible for a specific functionality and communicates with others via messaging systems.</t>
+          <t>La capa de presentació rep les peticions i construeix les respostes, la capa de lògica de negoci aplica les regles del domini, la capa d’accés a dades interactua amb la base de dades i la capa de domini defineix el model de dades. S’hi afegeix una capa transversal de contracte que separa el model intern de la representació externa de l’API.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.4517</v>
+        <v>0.7462</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M05_AU29</t>
+          <t>CF_M05_AU23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -893,44 +893,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>58</v>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M05_AU14, CF_M05_AU15</t>
+          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU06, CF_M05_AU07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>viewmodel, model</t>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AU_12</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ViewModel</t>
-        </is>
-      </c>
+          <t>AU_27</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Frontend component responsible for logic, data processing, and service orchestration (TS).</t>
+          <t>El microservei Communication Log té com a finalitat principal registrar totes les comunicacions que es produeixen dins del sistema, tant entre microserveis com amb serveis externs.</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.5221</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M05_AU30</t>
+          <t>CF_M05_AU24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -941,38 +939,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>The controllers, through specific
-functions, process the requests received, manage the validation of the information and channel
-the requests to the corresponding modules or services</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>61</v>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CF_AU17, CF_AU18</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>CF_M05_AU06, CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>client(frontend), server (backend)</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>The Leader Service routes communications to the Access Control Service.</t>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.2629</v>
+        <v>0.7956</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M05_AU31</t>
+          <t>CF_M05_AU25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -983,130 +989,143 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> the Repositories are responsible for performing queries on the database.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>Data access and logic management in this project is carried out using REST operations, which structure and normalize communication with the data layer.</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>69</v>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CF_AU21, CF_AU16</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>CF_M05_AU17, CF_M05_AU21</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>presentation layer (controllers), data access layer (repositories)</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Data Access Layer (Repository)</t>
-        </is>
-      </c>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Backend layer interacting with the database.</t>
+          <t>La capa de presentació rep les peticions i construeix les respostes, la capa de lògica de negoci aplica les regles del domini, la capa d’accés a dades interactua amb la base de dades i la capa de domini defineix el model de dades. S’hi afegeix una capa transversal de contracte que separa el model intern de la representació externa de l’API.</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.2089</v>
+        <v>0.7268</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CF_M05_AU32</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+          <t>CF_M05_AU26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>This technology helps us in the communication between the data layer and the database of the project application.</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>76</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU21, CF_M05_AU16</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>data access layer (repositories), database</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AU_17</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Capa d’accés a dades</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>La capa d’accés a dades interactua amb la base de dades.</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.7163</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CF_M05_AU28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>REST</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
 structure and normalize communication with the data layer. </t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E14" t="n">
         <v>69</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>The ViewModel orchestrates HTTP calls to the backend Presentation Layer.</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>0.0424</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CF_M05_AU35</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>The message
-exchange protocol used in this case is HTTP</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>62</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17, CF_M05_AU21</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AU_29</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>The ViewModel orchestrates HTTP calls to the backend Presentation Layer.</t>
+          <t>El protocol d’intercanvi de missatges que es fa servir en aquest cas és HTTP.</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.2782</v>
+        <v>0.6758999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CF_M05_AU37</t>
+          <t>CF_M05_AU32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1147,11 +1166,11 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>The application organizes code into two distinct components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.2932</v>
+        <v>0.7968</v>
       </c>
     </row>
     <row r="16">
@@ -1185,21 +1204,21 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_17</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Data Access Layer (Repository)</t>
+          <t>Capa d’accés a dades</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Backend layer interacting with the database.</t>
+          <t>La capa d’accés a dades interactua amb la base de dades.</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.0864</v>
+        <v>0.6917</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +523,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
+          <t>L’aplicació segueix el patró Client-Servidor el qual organitza el codi en dos components diferenciats: el client, que formula sol·licituds de servei, i el servidor, que les rep, les processa i retorna respostes.</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -565,7 +565,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_22</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>El proveïdor per aquest projecte és Amazon Web Services el qual té un ampli catàleg de serveis i recursos cloud.</t>
+          <t>Cloud provider for the system.</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -618,7 +618,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Pel desplegament de l’aplicació s’ha fet ús d’Amazon EKS, un servei que ofereix AWS el qual permet utilitzar Kubernetes (K8s).</t>
+          <t>Container orchestration platform used for deployment.</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -668,7 +668,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_21</t>
+          <t>AU_23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Pel desplegament de l’aplicació s’ha fet ús d’Amazon EKS, un servei que ofereix AWS el qual permet utilitzar Kubernetes (K8s).</t>
+          <t>Container orchestration platform used for deployment.</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -688,369 +688,381 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AU16</t>
+          <t>CF_M05_AU11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>These two microservices are responsible for
+calls to external services related to car sales.</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>60</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CF_M05_P01</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>The user is the actor that accesses the portal and applications.</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6729000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CF_M05_AU12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GSB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>These two microservices are responsible for
+calls to external services related to car sales.</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CF_M05_P01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>This microservice acts as a central point for traffic management and routing communications.</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6268</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>57</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AU_25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>The Leader microservice routes all communications to the corresponding microservice within the system architecture.</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9520999999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>58</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU06, CF_M05_AU07</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Communication Log</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>This microservice registers all communications within the system for traceability and auditing.</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7702</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU24</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>61</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU06, CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>client(frontend), server (backend)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>L’aplicació segueix el patró Client-Servidor el qual organitza el codi en dos components diferenciats: el client, que formula sol·licituds de servei, i el servidor, que les rep, les processa i retorna respostes.</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.7956</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU28</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
+structure and normalize communication with the data layer. </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>69</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17, CF_M05_AU21</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Communication protocol used for message exchange.</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6758999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Server (Backend)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
+responsibilities are separated:</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>68</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>L’aplicació segueix el patró Client-Servidor el qual organitza el codi en dos components diferenciats: el client, que formula sol·licituds de servei, i el servidor, que les rep, les processa i retorna respostes.</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7968</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M05_P06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Shared Database</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>61</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CF_M05_P06</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Capa d’accés a dades</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>La capa d’accés a dades interactua amb la base de dades.</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0.7621</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Presentation Layer (Controllers)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>The controllers, through specific
-functions, process the requests received, manage the validation of the information and channel
-the requests to the corresponding modules or services of the data layer.</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
+      <c r="E13" t="n">
         <v>60</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CF_M05_P04</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>La capa de presentació rep les peticions i construeix les respostes, la capa de lògica de negoci aplica les regles del domini, la capa d’accés a dades interactua amb la base de dades i la capa de domini defineix el model de dades. S’hi afegeix una capa transversal de contracte que separa el model intern de la representació externa de l’API.</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0.7357</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CF_M05_AU19</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Domain Layer (Models)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Models represent the internal and persistent structure of the system entities, reflecting the
-stored information identically.</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>71</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CF_M05_P04</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>La capa de presentació rep les peticions i construeix les respostes, la capa de lògica de negoci aplica les regles del domini, la capa d’accés a dades interactua amb la base de dades i la capa de domini defineix el model de dades. S’hi afegeix una capa transversal de contracte que separa el model intern de la representació externa de l’API.</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>0.7736</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CF_M05_AU20</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Contract Layer (DTO/Mappers)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
-request to be structured, providing a customized format based on response requirements.</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>73</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CF_M05_P04</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>La capa de presentació rep les peticions i construeix les respostes, la capa de lògica de negoci aplica les regles del domini, la capa d’accés a dades interactua amb la base de dades i la capa de domini defineix el model de dades. S’hi afegeix una capa transversal de contracte que separa el model intern de la representació externa de l’API.</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0.7462</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU23</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>58</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU06, CF_M05_AU07</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>AU_27</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>El microservei Communication Log té com a finalitat principal registrar totes les comunicacions que es produeixen dins del sistema, tant entre microserveis com amb serveis externs.</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M05_AU24</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>61</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CF_M05_AU06, CF_M05_AU32</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>client(frontend), server (backend)</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0.7956</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU25</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Data access and logic management in this project is carried out using REST operations, which structure and normalize communication with the data layer.</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>69</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17, CF_M05_AU21</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>presentation layer (controllers), data access layer (repositories)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>AU_24</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>La capa de presentació rep les peticions i construeix les respostes, la capa de lògica de negoci aplica les regles del domini, la capa d’accés a dades interactua amb la base de dades i la capa de domini defineix el model de dades. S’hi afegeix una capa transversal de contracte que separa el model intern de la representació externa de l’API.</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>0.7268</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CF_M05_AU26</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>This technology helps us in the communication between the data layer and the database of the project application.</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>76</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>CF_M05_AU21, CF_M05_AU16</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>data access layer (repositories), database</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
@@ -1059,166 +1071,16 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Capa d’accés a dades</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>La capa d’accés a dades interactua amb la base de dades.</t>
+          <t>Repositories are responsible for performing queries on the database.</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.7163</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CF_M05_AU28</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
-structure and normalize communication with the data layer. </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>69</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17, CF_M05_AU21</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>AU_10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>El protocol d’intercanvi de missatges que es fa servir en aquest cas és HTTP.</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>0.6758999999999999</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CF_M05_AU32</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Server (Backend)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
-responsibilities are separated:</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>68</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>CF_M05_P02</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>0.7968</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CF_M05_P06</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Shared Database</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>the microservices are connected to a shared database that is decoupled per
-microservice and client. There is a schema for each microservice and each client has its
-own set of schemas per microservice.</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>60</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Capa d’accés a dades</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>La capa d’accés a dades interactua amb la base de dades.</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>0.6917</v>
+        <v>0.6965</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +523,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>L’aplicació segueix el patró Client-Servidor el qual organitza el codi en dos components diferenciats: el client, que formula sol·licituds de servei, i el servidor, que les rep, les processa i retorna respostes.</t>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -533,12 +533,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M05_AU07</t>
+          <t>CF_M05_AU08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amazon EKS</t>
+          <t>SonarQube</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -547,58 +547,6 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
-which allows the use of Kubernetes (K8s), a container orchestration platform created by
-Google, without the need to install or maintain it. </t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>81</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CF_M05_P05</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Amazon Web Services</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Cloud provider for the system.</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0.7812</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CF_M05_AU08</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SonarQube</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
         <is>
           <t>SonarQube is a
 web application that statically analyses the code and offers recommendations and statistics
@@ -606,8 +554,58 @@
 problems, the amount of code covered in the tests, code duplication and code smells.</t>
         </is>
       </c>
+      <c r="E3" t="n">
+        <v>84</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Kubernetes</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Kubernetes is a container orchestration platform used for deployment.</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6439</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CF_M05_AU09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Grafana</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
+        </is>
+      </c>
       <c r="E4" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -618,7 +616,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -628,72 +626,73 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Container orchestration platform used for deployment.</t>
+          <t>Kubernetes is a container orchestration platform used for deployment.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.6439</v>
+        <v>0.6829</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AU09</t>
+          <t>CF_M05_AU11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grafana</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
+          <t>These two microservices are responsible for
+calls to external services related to car sales.</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M05_AU32</t>
+          <t>CF_M05_P01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_23</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Kubernetes</t>
+          <t>User</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Container orchestration platform used for deployment.</t>
+          <t>The user is the actor who accesses the portal and applications.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.6829</v>
+        <v>0.6729000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AU11</t>
+          <t>CF_M05_AU12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>GSB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -719,368 +718,517 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>The user is the actor that accesses the portal and applications.</t>
+          <t>This microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6268</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M05_AU12</t>
+          <t>CF_M05_AU14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GSB</t>
+          <t>ViewModel</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>These two microservices are responsible for
-calls to external services related to car sales.</t>
+          <t>The ViewModel component groups the TS files of the components and the services they
+have associated with them. Each TS file defines the behavior of the application component
+to which it corresponds, taking care of data processing and validations</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CF_M05_P01</t>
+          <t>CF_M05_P03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>MVVM</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>This microservice acts as a central point for traffic management and routing communications.</t>
+          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.6268</v>
+        <v>0.8874</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>CF_M05_AU15</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
+          <t>Models are the TypeScript classes that define the data contract consumed by the
+view and the ViewModel. These classes allow the View to know what data to display and
+the ViewModel to know how to manipulate it</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
-        </is>
-      </c>
+          <t>CF_M05_P03</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AU_25</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>The Leader microservice routes all communications to the corresponding microservice within the system architecture.</t>
+          <t>The user is the actor who accesses the portal and applications.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.7126</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M05_AU23</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>CF_M05_AU16</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Database</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>58</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU06, CF_M05_AU07</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>AU_11</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Communication Log</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>This microservice registers all communications within the system for traceability and auditing.</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0.7702</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU24</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>61</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU06, CF_M05_AU32</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>client(frontend), server (backend)</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>L’aplicació segueix el patró Client-Servidor el qual organitza el codi en dos components diferenciats: el client, que formula sol·licituds de servei, i el servidor, que les rep, les processa i retorna respostes.</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0.7956</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M05_AU28</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
-structure and normalize communication with the data layer. </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>69</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CF_M05_AU17, CF_M05_AU21</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Communication protocol used for message exchange.</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0.6758999999999999</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU32</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Server (Backend)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
-responsibilities are separated:</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>68</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CF_M05_P02</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>L’aplicació segueix el patró Client-Servidor el qual organitza el codi en dos components diferenciats: el client, que formula sol·licituds de servei, i el servidor, que les rep, les processa i retorna respostes.</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>0.7968</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CF_M05_P06</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Shared Database</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>60</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>61</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CF_M05_P06</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AU_05</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Data Access Layer</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>The data access layer interacts with the database.</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7631</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>57</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>The Leader microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0.9671</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>58</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU06, CF_M05_AU07</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>The Communication Log microservice has as its main purpose to record all communications that occur within the system, both between microservices and with external services.</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0.9822</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU24</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>61</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CF_M05_AU06, CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>client(frontend), server (backend)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.7956</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU27</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CF_M05_AU14, CF_M05_AU13, CF_M05_AU15</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>viewmodel, view, model</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>MVVM</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Repositories are responsible for performing queries on the database.</t>
+          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.6965</v>
+        <v>0.8110000000000001</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CF_M05_AU28</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>REST</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
+structure and normalize communication with the data layer. </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>69</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CF_M05_AU17, CF_M05_AU21</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>The exchange protocol used for communication between client and server.</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6758999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Server (Backend)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
+responsibilities are separated:</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>68</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CF_M05_P02</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.7968</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CF_M05_P06</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Shared Database</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>the microservices are connected to a shared database that is decoupled per
+microservice and client. There is a schema for each microservice and each client has its
+own set of schemas per microservice.</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>AU_05</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Data Access Layer</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>The data access layer interacts with the database.</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.6893</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,40 +513,88 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
+          <t>AU_21</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
+          <t>The client, which we also call frontEnd, is responsible for the presentation and user experience of the application, encapsulating the interface logic and the coordination of calls to the server's API.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.8405</v>
+        <v>0.8626</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>CF_M05_AU07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Amazon EKS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For the deployment of the application, Amazon EKS has been used, a service offered by AWS
+which allows the use of Kubernetes (K8s), a container orchestration platform created by
+Google, without the need to install or maintain it. </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>81</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CF_M05_P05</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Amazon Web Services</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>The provider for this project is Amazon Web Services which has a wide catalog of cloud services and resources.</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7812</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>CF_M05_AU08</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>SonarQube</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>SonarQube is a
 web application that statically analyses the code and offers recommendations and statistics
@@ -554,58 +602,8 @@
 problems, the amount of code covered in the tests, code duplication and code smells.</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>84</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CF_M05_AU32</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Kubernetes</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Kubernetes is a container orchestration platform used for deployment.</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>0.6439</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CF_M05_AU09</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Grafana</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>87</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -616,7 +614,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -626,73 +624,72 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Kubernetes is a container orchestration platform used for deployment.</t>
+          <t>Kubernetes is a container orchestration platform used for deployment via Amazon EKS.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.6829</v>
+        <v>0.6439</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M05_AU11</t>
+          <t>CF_M05_AU09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Grafana</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>These two microservices are responsible for
-calls to external services related to car sales.</t>
+          <t xml:space="preserve">For the tests, graphs were obtained with the help of Grafana. </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M05_P01</t>
+          <t>CF_M05_AU32</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Kubernetes</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>The user is the actor who accesses the portal and applications.</t>
+          <t>Kubernetes is a container orchestration platform used for deployment via Amazon EKS.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.6829</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AU12</t>
+          <t>CF_M05_AU11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GSB</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -718,275 +715,285 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>User</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>This microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
+          <t>The user is the actor who accesses the portal and applications.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.6268</v>
+        <v>0.6729000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>CF_M05_AU12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GSB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>These two microservices are responsible for
+calls to external services related to car sales.</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CF_M05_P01</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>AU_07</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>This microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6268</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>CF_M05_AU14</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>ViewModel</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>The ViewModel component groups the TS files of the components and the services they
 have associated with them. Each TS file defines the behavior of the application component
 to which it corresponds, taking care of data processing and validations</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E8" t="n">
         <v>64</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>MVVM</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>0.8874</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>CF_M05_AU15</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Models are the TypeScript classes that define the data contract consumed by the
 view and the ViewModel. These classes allow the View to know what data to display and
 the ViewModel to know how to manipulate it</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E9" t="n">
         <v>66</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>The user is the actor who accesses the portal and applications.</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="L9" t="n">
         <v>0.7126</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>CF_M05_AU16</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Database</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" t="n">
         <v>61</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>CF_M05_P06</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Data Access Layer</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>The data access layer interacts with the database.</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0.7631</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>57</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AU_20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>AU_05</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Data Access Layer</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>The Leader microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
+          <t>The data access layer interacts with the database.</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.9671</v>
+        <v>0.7631</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M05_AU23</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>CF_M05_AU20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Contract Layer (DTO/Mappers)</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
+          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
+request to be structured, providing a customized format based on response requirements.</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU06, CF_M05_AU07</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
-        </is>
-      </c>
+          <t>CF_M05_P04</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AU_22</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>AU_04</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Business Logic Layer</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>The Communication Log microservice has as its main purpose to record all communications that occur within the system, both between microservices and with external services.</t>
+          <t>The business logic layer applies the domain rules.</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.9822</v>
+        <v>0.7371</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M05_AU24</t>
+          <t>CF_M05_AU22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -997,46 +1004,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
+          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CF_M05_AU06, CF_M05_AU32</t>
+          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>client(frontend), server (backend)</t>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
+          <t>The Leader microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.7956</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CF_M05_AU27</t>
+          <t>CF_M05_AU23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1047,187 +1050,283 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>58</v>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CF_M05_AU14, CF_M05_AU13, CF_M05_AU15</t>
+          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU06, CF_M05_AU07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>viewmodel, view, model</t>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>MVVM</t>
-        </is>
-      </c>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
+          <t>The Communication Log microservice has as its main purpose to record all communications that occur within the system, both between microservices and with external services.</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.9822</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>CF_M05_AU24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>61</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CF_M05_AU06, CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>client(frontend), server (backend)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.7956</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CF_M05_AU27</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CF_M05_AU14, CF_M05_AU13, CF_M05_AU15</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>viewmodel, view, model</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MVVM</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>CF_M05_AU28</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>REST</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
 structure and normalize communication with the data layer. </t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E16" t="n">
         <v>69</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>CF_M05_AU17, CF_M05_AU21</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>HTTP</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>The exchange protocol used for communication between client and server.</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>The message exchange protocol used in this case is HTTP.</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
         <v>0.6758999999999999</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Server (Backend)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
 responsibilities are separated:</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E17" t="n">
         <v>68</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
         </is>
       </c>
-      <c r="L15" t="n">
+      <c r="L17" t="n">
         <v>0.7968</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>CF_M05_P06</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Shared Database</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Design Pattern</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E18" t="n">
         <v>60</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Data Access Layer</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>The data access layer interacts with the database.</t>
         </is>
       </c>
-      <c r="L16" t="n">
+      <c r="L18" t="n">
         <v>0.6893</v>
       </c>
     </row>

--- a/outputs/evaluation/architecture/CF_M05_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/CF_M05_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,7 +454,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>GT_fixes</t>
+          <t>GT_fixedType</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
@@ -513,17 +513,21 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_21</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>The client, which we also call frontEnd, is responsible for the presentation and user experience of the application, encapsulating the interface logic and the coordination of calls to the server's API.</t>
+          <t>The client, which we also call frontEnd, is responsible for the presentation and user experience of the application.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.8626</v>
+        <v>0.8573</v>
       </c>
     </row>
     <row r="3">
@@ -561,7 +565,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -571,7 +575,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>The provider for this project is Amazon Web Services which has a wide catalog of cloud services and resources.</t>
+          <t>The provider for this project is Amazon Web Services.</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -614,7 +618,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -624,7 +628,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Kubernetes is a container orchestration platform used for deployment via Amazon EKS.</t>
+          <t>Kubernetes is a container orchestration platform used for deployment.</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -664,7 +668,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -674,7 +678,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Kubernetes is a container orchestration platform used for deployment via Amazon EKS.</t>
+          <t>Kubernetes is a container orchestration platform used for deployment.</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -684,63 +688,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M05_AU11</t>
+          <t>CF_M05_AU10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ordering</t>
+          <t>Amazon RDS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>These two microservices are responsible for
-calls to external services related to car sales.</t>
+          <t xml:space="preserve"> the microservices are connected to a shared database (Amazon RDS) that is decoupled per
+microservice and client. </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CF_M05_P01</t>
+          <t>CF_M05_P05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Amazon Web Services</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>The user is the actor who accesses the portal and applications.</t>
+          <t>The provider for this project is Amazon Web Services.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.8105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M05_AU12</t>
+          <t>CF_M05_AU11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GSB</t>
+          <t>Ordering</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -766,280 +770,282 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>User</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>This microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
+          <t>The user is the actor who accesses the portal and applications.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.6268</v>
+        <v>0.6729000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>CF_M05_AU12</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GSB</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>These two microservices are responsible for
+calls to external services related to car sales.</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CF_M05_P01</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>This microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6268</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CF_M05_AU13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>The component we call View, Vista in Catalan, is made up of the HTML and SCSS files of
+each component that makes up the application. They are responsible for presenting the
+screens and capturing user interactions such as clicks or text entries.</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>62</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CF_M05_P03</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>The user is the actor who accesses the portal and applications.</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7551</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>CF_M05_AU14</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>ViewModel</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>The ViewModel component groups the TS files of the components and the services they
 have associated with them. Each TS file defines the behavior of the application component
 to which it corresponds, taking care of data processing and validations</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E10" t="n">
         <v>64</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>MVVM</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="L10" t="n">
         <v>0.8874</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>CF_M05_AU15</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Models are the TypeScript classes that define the data contract consumed by the
 view and the ViewModel. These classes allow the View to know what data to display and
 the ViewModel to know how to manipulate it</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>66</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>CF_M05_P03</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>User</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>The user is the actor who accesses the portal and applications.</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="L11" t="n">
         <v>0.7126</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>CF_M05_AU16</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Database</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E12" t="n">
         <v>61</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>CF_M05_P06</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Data Access Layer</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>The data access layer interacts with the database.</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0.7631</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CF_M05_AU20</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Contract Layer (DTO/Mappers)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Layer</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Data Transfer Objects (DTOs) act as information containers that allow the data required for each
-request to be structured, providing a customized format based on response requirements.</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>73</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>CF_M05_P04</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>AU_04</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Business Logic Layer</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>The business logic layer applies the domain rules.</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>0.7371</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU22</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>57</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>The Leader microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
+          <t>The data access layer interacts with the database.</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.9671</v>
+        <v>0.7869</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CF_M05_AU23</t>
+          <t>CF_M05_AU22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1050,42 +1056,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
+          <t>Leader's main function is to route all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU06, CF_M05_AU07</t>
+          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU11, CF_M05_AU12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, ordering, gsb</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AU_20</t>
+          <t>AU_21</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>The Communication Log microservice has as its main purpose to record all communications that occur within the system, both between microservices and with external services.</t>
+          <t>The Leader microservice has as its main function the routing of all communications to the corresponding microservice within the system architecture.</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.9822</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CF_M05_AU24</t>
+          <t>CF_M05_AU23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -1096,46 +1102,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Communication between the two components [client-server] is done through an exchange of messages following standard network protocols and making use of interoperable data representation formats.</t>
+          <t>Communication Log's main purpose is to record all communications that occur within the system, both between microservices and with external services.</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CF_M05_AU06, CF_M05_AU32</t>
+          <t>CF_M05_AU01, CF_M05_AU02, CF_M05_AU03, CF_M05_AU04, CF_M05_AU05, CF_M05_AU06, CF_M05_AU07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>client(frontend), server (backend)</t>
+          <t>leader microservice, portal microservice, access control microservice, communication log microservice, scheduler microservice, client(frontend), amazon eks</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Communication Log</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
+          <t>The Communication Log microservice has as its main purpose to record all communications that occur within the system.</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0.7956</v>
+        <v>0.7702</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CF_M05_AU27</t>
+          <t>CF_M05_AU25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -1146,188 +1152,271 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>Data access and logic management in this project is carried out using REST operations, which structure and normalize communication with the data layer.</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>69</v>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CF_M05_AU14, CF_M05_AU13, CF_M05_AU15</t>
+          <t>CF_M05_AU17, CF_M05_AU21</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>viewmodel, view, model</t>
+          <t>presentation layer (controllers), data access layer (repositories)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>MVVM</t>
-        </is>
-      </c>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
+          <t>The data access layer interacts with the database.</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.7479</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CF_M05_AU28</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>REST</t>
-        </is>
-      </c>
+          <t>CF_M05_AU26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data access and logic management in this project is carried out through REST operations, which
-structure and normalize communication with the data layer. </t>
+          <t>This technology helps us in the communication between the data layer and the database of the project application.</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CF_M05_AU17, CF_M05_AU21</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>CF_M05_AU21, CF_M05_AU16</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>data access layer (repositories), database</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>The message exchange protocol used in this case is HTTP.</t>
+          <t>The data access layer interacts with the database.</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.8274</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>CF_M05_AU27</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ViewModel acts as an intermediary between the View and the Model </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CF_M05_AU14, CF_M05_AU13, CF_M05_AU15</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>viewmodel, view, model</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AU_22</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>The client, which we also call frontEnd, is responsible for the presentation and user experience of the application. [...] The ViewModel acts as an intermediary between the View and the Model, providing the data that the view needs and managing the user's actions.</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.8557</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>CF_M05_AU32</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Server (Backend)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>For the server, the backEnd, Spring Boot organizes the code following the pattern of layers with which
 responsibilities are separated:</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E18" t="n">
         <v>68</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>CF_M05_P02</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Client-Server</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>The application follows the Client-Server pattern which organizes the code into two differentiated components: the client, which formulates service requests, and the server, which receives, processes, and returns responses.</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>0.7968</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>AU_14</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>For the server, the backEnd, Spring Boot organizes the code following the layered pattern.</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.9097</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CF_M05_AU33</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Docker</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>The deployment process for our application begins with the creation of a Docker image [28] for each microservice which has its own repository with a Dockerfile [29].</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>81</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CF_M05_AU32</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>AU_20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Kubernetes</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Kubernetes is a container orchestration platform used for deployment.</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.7665</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>CF_M05_P06</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Shared Database</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Design Pattern</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>the microservices are connected to a shared database that is decoupled per
 microservice and client. There is a schema for each microservice and each client has its
 own set of schemas per microservice.</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E20" t="n">
         <v>60</v>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>AU_05</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Data Access Layer</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>AU_24</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
         <is>
           <t>The data access layer interacts with the database.</t>
         </is>
       </c>
-      <c r="L18" t="n">
-        <v>0.6893</v>
+      <c r="L20" t="n">
+        <v>0.7251</v>
       </c>
     </row>
   </sheetData>
